--- a/product-updates/Court_Ready_Master_Index.xlsx
+++ b/product-updates/Court_Ready_Master_Index.xlsx
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="D6" s="7">
-        <f>SUM(Expense!F5:F1000)</f>
+        <f>SUM(Expense!G5:G1000)</f>
         <v/>
       </c>
     </row>

--- a/product-updates/Court_Ready_Master_Index.xlsx
+++ b/product-updates/Court_Ready_Master_Index.xlsx
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G5" s="13" t="inlineStr">
         <is>
-          <t>2026-07-18_Screenshot_EVT-0001_ExA.png</t>
+          <t>EVT-0001_2026-07-18_Exchange_ExA_Screenshot.png</t>
         </is>
       </c>
       <c r="H5" s="13" t="inlineStr">
